--- a/博客访问量记录.xlsx
+++ b/博客访问量记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzp\Desktop\HexoBlog\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C4119F-F615-41AC-A227-692161A539C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE769E5E-3CBD-429F-8D4C-D39815004E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="22552" windowHeight="12175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="751" yWindow="751" windowWidth="16756" windowHeight="8683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>2022.4.18</t>
   </si>
@@ -137,6 +137,10 @@
   </si>
   <si>
     <t>2025.9.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.10.27</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -472,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.07421875" customWidth="1"/>
@@ -525,7 +529,7 @@
         <v>60946</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C24" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C25" si="0">B4-B3</f>
         <v>4080</v>
       </c>
     </row>
@@ -767,6 +771,18 @@
       <c r="C24">
         <f t="shared" si="0"/>
         <v>21244</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25">
+        <v>318816</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>5851</v>
       </c>
     </row>
   </sheetData>
